--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6472-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6472-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF1CBE69-A1E7-4631-90BD-95D8096C20D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A2A00E5-82AC-4C52-93B6-CE4A0255B0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F8230735-4CE0-47D9-A64E-0A20BC54D9E7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{593B7C96-6E90-4FAE-935C-16F6E0592CE2}"/>
   </bookViews>
   <sheets>
     <sheet name="6472-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1553,25 +1553,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5196DCD-2968-4656-9453-BCD4DF506E31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E81848DC-1439-4FBA-9ABC-1142B0D9B167}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.25" customWidth="1"/>
+    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1599,7 +1599,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1725,7 +1725,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>2025</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="45" t="s">
         <v>26</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="46"/>
       <c r="B10" s="22" t="s">
         <v>29</v>
@@ -2023,7 +2023,7 @@
       <c r="Q10" s="50"/>
       <c r="R10" s="50"/>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <v>2024</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="43">
         <v>2023</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="45" t="s">
         <v>26</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="46"/>
       <c r="B18" s="22" t="s">
         <v>35</v>
@@ -2433,7 +2433,7 @@
       <c r="Q18" s="50"/>
       <c r="R18" s="50"/>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2022</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="55" t="s">
         <v>26</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="56"/>
       <c r="B22" s="24" t="s">
         <v>38</v>
@@ -2621,7 +2621,7 @@
       <c r="Q22" s="60"/>
       <c r="R22" s="60"/>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="43">
         <v>2021</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>2020</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="55" t="s">
         <v>26</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="24" t="s">
         <v>44</v>
@@ -2975,7 +2975,7 @@
       <c r="Q29" s="60"/>
       <c r="R29" s="60"/>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <v>2019</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>2018</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="43">
         <v>2017</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>2016</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="43">
         <v>2015</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="41" t="s">
         <v>45</v>
       </c>
